--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>13.77939726727322</v>
+        <v>2.239152055931899</v>
       </c>
       <c r="D2" t="n">
-        <v>14.16318405342493</v>
+        <v>2.301517408681552</v>
       </c>
       <c r="E2" t="n">
-        <v>15.94672065289059</v>
+        <v>2.591342106094721</v>
       </c>
       <c r="F2" t="n">
-        <v>16.00250408137182</v>
+        <v>2.600406913222921</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.31695937583357</v>
+        <v>6.551505898572955</v>
       </c>
       <c r="D3" t="n">
-        <v>40.6077461412557</v>
+        <v>6.598758747954051</v>
       </c>
       <c r="E3" t="n">
-        <v>15.94672065289059</v>
+        <v>2.591342106094721</v>
       </c>
       <c r="F3" t="n">
-        <v>16.00250408137182</v>
+        <v>2.600406913222921</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.46031355003551</v>
+        <v>2.51230095188077</v>
       </c>
       <c r="D4" t="n">
-        <v>15.18816393132995</v>
+        <v>2.468076638841118</v>
       </c>
       <c r="E4" t="n">
-        <v>15.94672065289059</v>
+        <v>2.591342106094721</v>
       </c>
       <c r="F4" t="n">
-        <v>16.00250408137182</v>
+        <v>2.600406913222921</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.94023756618263</v>
+        <v>8.602788604504678</v>
       </c>
       <c r="D5" t="n">
-        <v>53.07935452734001</v>
+        <v>8.625395110692752</v>
       </c>
       <c r="E5" t="n">
-        <v>15.94672065289059</v>
+        <v>2.591342106094721</v>
       </c>
       <c r="F5" t="n">
-        <v>16.00250408137182</v>
+        <v>2.600406913222921</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.2261563414594</v>
+        <v>2.636750405487152</v>
       </c>
       <c r="D6" t="n">
-        <v>16.29704771751985</v>
+        <v>2.648270254096975</v>
       </c>
       <c r="E6" t="n">
-        <v>15.94672065289059</v>
+        <v>2.591342106094721</v>
       </c>
       <c r="F6" t="n">
-        <v>16.00250408137182</v>
+        <v>2.600406913222921</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
